--- a/research/traditional_assets/database/data/taiwan/taiwan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.214</v>
+        <v>0.0296</v>
       </c>
       <c r="E2">
-        <v>0.268</v>
+        <v>-0.0378</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>841.6</v>
+        <v>201.457</v>
       </c>
       <c r="L2">
-        <v>0.4004377408764334</v>
+        <v>0.2140449856033319</v>
       </c>
       <c r="M2">
-        <v>362.3958</v>
+        <v>357.1968</v>
       </c>
       <c r="N2">
-        <v>0.04908317419040267</v>
+        <v>0.09589433273376466</v>
       </c>
       <c r="O2">
-        <v>0.4306033745247148</v>
+        <v>1.773067205408598</v>
       </c>
       <c r="P2">
-        <v>362.3958</v>
+        <v>357.1968</v>
       </c>
       <c r="Q2">
-        <v>0.04908317419040267</v>
+        <v>0.09589433273376466</v>
       </c>
       <c r="R2">
-        <v>0.4306033745247148</v>
+        <v>1.773067205408598</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2220.11</v>
+        <v>1326.77</v>
       </c>
       <c r="V2">
-        <v>0.3006934568553357</v>
+        <v>0.3561894279041048</v>
       </c>
       <c r="W2">
-        <v>0.1603563474387528</v>
+        <v>0.03562130934776327</v>
       </c>
       <c r="X2">
-        <v>0.04772737894626963</v>
+        <v>0.09002603668249065</v>
       </c>
       <c r="Y2">
-        <v>0.1126289684924832</v>
+        <v>-0.05440472733472738</v>
       </c>
       <c r="Z2">
-        <v>0.1253154425867511</v>
+        <v>0.05717737707963504</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03761254573753203</v>
+        <v>0.07039726900506925</v>
       </c>
       <c r="AC2">
-        <v>-0.03761254573753203</v>
+        <v>-0.07039726900506925</v>
       </c>
       <c r="AD2">
-        <v>14418.28</v>
+        <v>10082.152</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>14418.28</v>
+        <v>10082.152</v>
       </c>
       <c r="AG2">
-        <v>12198.17</v>
+        <v>8755.382</v>
       </c>
       <c r="AH2">
-        <v>0.6613410587673003</v>
+        <v>0.7302175728750786</v>
       </c>
       <c r="AI2">
-        <v>0.6650811062144069</v>
+        <v>0.6969140211014808</v>
       </c>
       <c r="AJ2">
-        <v>0.6229445491068852</v>
+        <v>0.7015371928294569</v>
       </c>
       <c r="AK2">
-        <v>0.6268693916964346</v>
+        <v>0.6663110625945866</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yuanta Futures Co., Ltd. (TPEX:6023)</t>
+          <t>China Bills Finance Corporation (TWSE:2820)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0605</v>
+        <v>-0.0247</v>
       </c>
       <c r="E3">
-        <v>0.0235</v>
+        <v>0.00136</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>33.6</v>
+        <v>42.1</v>
       </c>
       <c r="L3">
-        <v>0.2367864693446089</v>
+        <v>0.7246127366609294</v>
       </c>
       <c r="M3">
-        <v>29.2</v>
+        <v>38</v>
       </c>
       <c r="N3">
-        <v>0.05608912792931233</v>
+        <v>0.05994636377977599</v>
       </c>
       <c r="O3">
-        <v>0.869047619047619</v>
+        <v>0.9026128266033254</v>
       </c>
       <c r="P3">
-        <v>29.2</v>
+        <v>38</v>
       </c>
       <c r="Q3">
-        <v>0.05608912792931233</v>
+        <v>0.05994636377977599</v>
       </c>
       <c r="R3">
-        <v>0.869047619047619</v>
+        <v>0.9026128266033254</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>281.9</v>
+        <v>35.2</v>
       </c>
       <c r="V3">
-        <v>0.5414905877833268</v>
+        <v>0.05552926329073987</v>
       </c>
       <c r="W3">
-        <v>0.09958506224066391</v>
+        <v>0.04612182296231376</v>
       </c>
       <c r="X3">
-        <v>0.0361946171315095</v>
+        <v>0.2923229965925215</v>
       </c>
       <c r="Y3">
-        <v>0.0633904451091544</v>
+        <v>-0.2462011736302077</v>
       </c>
       <c r="Z3">
-        <v>1.04870297834602</v>
+        <v>0.006762419107034778</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03602355853254019</v>
+        <v>0.06922506371491288</v>
       </c>
       <c r="AC3">
-        <v>-0.03602355853254019</v>
+        <v>-0.06922506371491288</v>
       </c>
       <c r="AD3">
-        <v>6.73</v>
+        <v>5542.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.73</v>
+        <v>5542.1</v>
       </c>
       <c r="AG3">
-        <v>-275.17</v>
+        <v>5506.900000000001</v>
       </c>
       <c r="AH3">
-        <v>0.01276240684201544</v>
+        <v>0.8973607512953369</v>
       </c>
       <c r="AI3">
-        <v>0.01532226851535642</v>
+        <v>0.8907121389884444</v>
       </c>
       <c r="AJ3">
-        <v>-1.12117508047101</v>
+        <v>0.8967724075039083</v>
       </c>
       <c r="AK3">
-        <v>-1.748998919468632</v>
+        <v>0.8900903521957685</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital Futures Corporation (TWSE:6024)</t>
+          <t>Capital Securities Corporation (TWSE:6005)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0353</v>
+        <v>0.0405</v>
       </c>
       <c r="E4">
-        <v>0.0161</v>
+        <v>-0.04849999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>19.2</v>
+        <v>52.3</v>
       </c>
       <c r="L4">
-        <v>0.2157303370786517</v>
+        <v>0.1842847075405215</v>
       </c>
       <c r="M4">
-        <v>21.7</v>
+        <v>117.3</v>
       </c>
       <c r="N4">
-        <v>0.07343485617597292</v>
+        <v>0.1529933481152993</v>
       </c>
       <c r="O4">
-        <v>1.130208333333333</v>
+        <v>2.24282982791587</v>
       </c>
       <c r="P4">
-        <v>21.7</v>
+        <v>117.3</v>
       </c>
       <c r="Q4">
-        <v>0.07343485617597292</v>
+        <v>0.1529933481152993</v>
       </c>
       <c r="R4">
-        <v>1.130208333333333</v>
+        <v>2.24282982791587</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>183.1</v>
+        <v>366.1</v>
       </c>
       <c r="V4">
-        <v>0.6196277495769882</v>
+        <v>0.4775009782183383</v>
       </c>
       <c r="W4">
-        <v>0.08913649025069638</v>
+        <v>0.0387120651369356</v>
       </c>
       <c r="X4">
-        <v>0.03650210724165233</v>
+        <v>0.1553998164405579</v>
       </c>
       <c r="Y4">
-        <v>0.05263438300904405</v>
+        <v>-0.1166877513036223</v>
       </c>
       <c r="Z4">
-        <v>2.162451101878174</v>
+        <v>0.08271399842616071</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.036085510298892</v>
+        <v>0.06940800634900479</v>
       </c>
       <c r="AC4">
-        <v>-0.036085510298892</v>
+        <v>-0.06940800634900479</v>
       </c>
       <c r="AD4">
-        <v>9.26</v>
+        <v>2565.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>9.26</v>
+        <v>2565.3</v>
       </c>
       <c r="AG4">
-        <v>-173.84</v>
+        <v>2199.2</v>
       </c>
       <c r="AH4">
-        <v>0.03038456490353065</v>
+        <v>0.7698979591836735</v>
       </c>
       <c r="AI4">
-        <v>0.04002420470262794</v>
+        <v>0.6850299081392865</v>
       </c>
       <c r="AJ4">
-        <v>-1.42890021371034</v>
+        <v>0.7414949930881014</v>
       </c>
       <c r="AK4">
-        <v>-3.602154993783672</v>
+        <v>0.6509012342025039</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reliance Securities Co.,Ltd. (TPEX:6027)</t>
+          <t>President Securities Corporation (TWSE:2855)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,7 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.402</v>
+        <v>0.033</v>
+      </c>
+      <c r="E5">
+        <v>-0.0592</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,82 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>12</v>
+        <v>36.2</v>
       </c>
       <c r="L5">
-        <v>0.5633802816901409</v>
+        <v>0.173621103117506</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1167745415318231</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>2.392265193370165</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1167745415318231</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>2.392265193370165</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>6.72</v>
+        <v>202.5</v>
       </c>
       <c r="V5">
-        <v>0.1520361990950226</v>
+        <v>0.2730582524271845</v>
       </c>
       <c r="W5">
-        <v>0.2649006622516556</v>
+        <v>0.03253055355859095</v>
       </c>
       <c r="X5">
-        <v>0.03782659742638778</v>
+        <v>0.09970129960236448</v>
       </c>
       <c r="Y5">
-        <v>0.2270740648252679</v>
+        <v>-0.06717074604377354</v>
       </c>
       <c r="Z5">
-        <v>0.4390847247990106</v>
+        <v>0.1046902223851295</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03669688291675888</v>
+        <v>0.06974516290661031</v>
       </c>
       <c r="AC5">
-        <v>-0.03669688291675888</v>
+        <v>-0.06974516290661031</v>
       </c>
       <c r="AD5">
-        <v>4.89</v>
+        <v>853.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>4.89</v>
+        <v>853.2</v>
       </c>
       <c r="AG5">
-        <v>-1.83</v>
+        <v>650.7</v>
       </c>
       <c r="AH5">
-        <v>0.09961295579547769</v>
+        <v>0.5349887133182843</v>
       </c>
       <c r="AI5">
-        <v>0.0723479804704838</v>
+        <v>0.4790567097136441</v>
       </c>
       <c r="AJ5">
-        <v>-0.04319093698371489</v>
+        <v>0.4673561732385261</v>
       </c>
       <c r="AK5">
-        <v>-0.03006407097092164</v>
+        <v>0.4122267975926513</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1061,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TaChan Securities Co.,Ltd. (TPEX:6020)</t>
+          <t>Good Finance Securities Co., Ltd. (TPEX:6021)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1070,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.393</v>
+        <v>0.122</v>
       </c>
       <c r="E6">
-        <v>0.504</v>
+        <v>-0.0443</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1088,85 +1094,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>26.2</v>
+        <v>3.34</v>
       </c>
       <c r="L6">
-        <v>0.6770025839793281</v>
+        <v>0.1113333333333333</v>
       </c>
       <c r="M6">
-        <v>6.55</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03056462902473168</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.25</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>6.55</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.03056462902473168</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.25</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>80.8</v>
+        <v>24.7</v>
       </c>
       <c r="V6">
-        <v>0.377041530564629</v>
+        <v>0.1218549580661075</v>
       </c>
       <c r="W6">
-        <v>0.1880832735104092</v>
+        <v>0.01674185463659148</v>
       </c>
       <c r="X6">
-        <v>0.04188668896673906</v>
+        <v>0.0803507737626168</v>
       </c>
       <c r="Y6">
-        <v>0.1461965845436701</v>
+        <v>-0.06360891912602533</v>
       </c>
       <c r="Z6">
-        <v>0.2415730337078652</v>
+        <v>0.09406157898037248</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03689726959709234</v>
+        <v>0.07011197555071585</v>
       </c>
       <c r="AC6">
-        <v>-0.03689726959709234</v>
+        <v>-0.07011197555071585</v>
       </c>
       <c r="AD6">
-        <v>75.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>75.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AG6">
-        <v>-5</v>
+        <v>53.89999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.2612892106170286</v>
+        <v>0.2794169925346605</v>
       </c>
       <c r="AI6">
-        <v>0.3125773195876289</v>
+        <v>0.3504235399019171</v>
       </c>
       <c r="AJ6">
-        <v>-0.02388915432393693</v>
+        <v>0.2100545596258769</v>
       </c>
       <c r="AK6">
-        <v>-0.03092145949288807</v>
+        <v>0.2700400801603207</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1183,7 +1186,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Good Finance Securities Co., Ltd. (TPEX:6021)</t>
+          <t>TaChan Securities Co.,Ltd. (TPEX:6020)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1192,7 +1195,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.277</v>
+        <v>-0.07690000000000001</v>
+      </c>
+      <c r="E7">
+        <v>-0.64</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1207,82 +1213,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>0.037</v>
       </c>
       <c r="L7">
-        <v>0.267260579064588</v>
+        <v>0.005727554179566563</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>18.9</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.1236910994764398</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>510.8108108108108</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>18.9</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.1236910994764398</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>510.8108108108108</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>14.4</v>
+        <v>53.4</v>
       </c>
       <c r="V7">
-        <v>0.0602258469259724</v>
+        <v>0.3494764397905759</v>
       </c>
       <c r="W7">
-        <v>0.07402837754472548</v>
+        <v>0.0002219556088782244</v>
       </c>
       <c r="X7">
-        <v>0.04545836843437411</v>
+        <v>0.07979446476153527</v>
       </c>
       <c r="Y7">
-        <v>0.02857000911035137</v>
+        <v>-0.07957250915265705</v>
       </c>
       <c r="Z7">
-        <v>0.2509501453163425</v>
+        <v>0.03995052566481138</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03725153459865326</v>
+        <v>0.07012857925631025</v>
       </c>
       <c r="AC7">
-        <v>-0.03725153459865326</v>
+        <v>-0.07012857925631025</v>
       </c>
       <c r="AD7">
-        <v>135.7</v>
+        <v>55.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>135.7</v>
+        <v>55.9</v>
       </c>
       <c r="AG7">
-        <v>121.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH7">
-        <v>0.362059765208111</v>
+        <v>0.2678485864877815</v>
       </c>
       <c r="AI7">
-        <v>0.4048329355608591</v>
+        <v>0.3052976515565265</v>
       </c>
       <c r="AJ7">
-        <v>0.3365704772475028</v>
+        <v>0.01609787508048937</v>
       </c>
       <c r="AK7">
-        <v>0.3781172069825436</v>
+        <v>0.01927525057825752</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1299,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grand Fortune Securities Co.,Ltd (TPEX:6026)</t>
+          <t>Yuanta Futures Co., Ltd. (TPEX:6023)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1308,10 +1317,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.271</v>
+        <v>0.0604</v>
       </c>
       <c r="E8">
-        <v>0.279</v>
+        <v>0.0282</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1326,28 +1335,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>39.6</v>
+        <v>29.9</v>
       </c>
       <c r="L8">
-        <v>0.5901639344262296</v>
+        <v>0.2521079258010118</v>
       </c>
       <c r="M8">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="N8">
-        <v>0.006053268765133172</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="O8">
-        <v>0.03787878787878788</v>
+        <v>0.7023411371237459</v>
       </c>
       <c r="P8">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="Q8">
-        <v>0.006053268765133172</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="R8">
-        <v>0.03787878787878788</v>
+        <v>0.7023411371237459</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1356,55 +1365,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>9.359999999999999</v>
+        <v>298.5</v>
       </c>
       <c r="V8">
-        <v>0.03777239709443099</v>
+        <v>0.6461038961038961</v>
       </c>
       <c r="W8">
-        <v>0.3746452223273415</v>
+        <v>0.06913294797687861</v>
       </c>
       <c r="X8">
-        <v>0.04772737894626963</v>
+        <v>0.07337953926997595</v>
       </c>
       <c r="Y8">
-        <v>0.3269178433810719</v>
+        <v>-0.004246591293097346</v>
       </c>
       <c r="Z8">
-        <v>0.4698879551820728</v>
+        <v>0.7538295302866583</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03743039071162602</v>
+        <v>0.07036730894981515</v>
       </c>
       <c r="AC8">
-        <v>-0.03743039071162602</v>
+        <v>-0.07036730894981515</v>
       </c>
       <c r="AD8">
-        <v>174.3</v>
+        <v>52.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>174.3</v>
+        <v>52.2</v>
       </c>
       <c r="AG8">
-        <v>164.94</v>
+        <v>-246.3</v>
       </c>
       <c r="AH8">
-        <v>0.4129353233830846</v>
+        <v>0.1015169194865811</v>
       </c>
       <c r="AI8">
-        <v>0.4904333145751267</v>
+        <v>0.1166219839142091</v>
       </c>
       <c r="AJ8">
-        <v>0.3996220380869313</v>
+        <v>-1.141863699582754</v>
       </c>
       <c r="AK8">
-        <v>0.4766500982545371</v>
+        <v>-1.651911468812878</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1421,7 +1430,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>President Securities Corporation (TWSE:2855)</t>
+          <t>Capital Futures Corporation (TWSE:6024)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1430,10 +1439,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.214</v>
+        <v>0.00544</v>
       </c>
       <c r="E9">
-        <v>0.305</v>
+        <v>-0.0159</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1448,28 +1457,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>182.2</v>
+        <v>20</v>
       </c>
       <c r="L9">
-        <v>0.4136208853575482</v>
+        <v>0.2447980416156671</v>
       </c>
       <c r="M9">
-        <v>75.40000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="N9">
-        <v>0.06074276967695159</v>
+        <v>0.04211362733412793</v>
       </c>
       <c r="O9">
-        <v>0.4138309549945116</v>
+        <v>0.53</v>
       </c>
       <c r="P9">
-        <v>75.40000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="Q9">
-        <v>0.06074276967695159</v>
+        <v>0.04211362733412793</v>
       </c>
       <c r="R9">
-        <v>0.4138309549945116</v>
+        <v>0.53</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1478,55 +1487,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>197.5</v>
+        <v>175.4</v>
       </c>
       <c r="V9">
-        <v>0.1591073874164183</v>
+        <v>0.6968613428684943</v>
       </c>
       <c r="W9">
-        <v>0.1909452944875288</v>
+        <v>0.09045680687471733</v>
       </c>
       <c r="X9">
-        <v>0.05048158604109789</v>
+        <v>0.07212575203915733</v>
       </c>
       <c r="Y9">
-        <v>0.1404637084464309</v>
+        <v>0.01833105483556</v>
       </c>
       <c r="Z9">
-        <v>0.197821937801729</v>
+        <v>1.751677708453936</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03761254573753203</v>
+        <v>0.07042722906032335</v>
       </c>
       <c r="AC9">
-        <v>-0.03761254573753203</v>
+        <v>-0.07042722906032335</v>
       </c>
       <c r="AD9">
-        <v>1077.8</v>
+        <v>16</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1077.8</v>
+        <v>16</v>
       </c>
       <c r="AG9">
-        <v>880.3</v>
+        <v>-159.4</v>
       </c>
       <c r="AH9">
-        <v>0.4647492561769652</v>
+        <v>0.05976839745984311</v>
       </c>
       <c r="AI9">
-        <v>0.4913832406309839</v>
+        <v>0.07191011235955057</v>
       </c>
       <c r="AJ9">
-        <v>0.4149226998491704</v>
+        <v>-1.726977248104009</v>
       </c>
       <c r="AK9">
-        <v>0.4410541610301117</v>
+        <v>-3.384288747346073</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1543,7 +1552,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Concord International Securities Co., Ltd (TPEX:5864)</t>
+          <t>Reliance Securities Co.,Ltd. (TPEX:6027)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1552,10 +1561,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.296</v>
-      </c>
-      <c r="E10">
-        <v>0.524</v>
+        <v>0.105</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1570,85 +1576,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>26.9</v>
+        <v>-1.55</v>
       </c>
       <c r="L10">
-        <v>0.6915167095115681</v>
+        <v>-0.2753108348134991</v>
       </c>
       <c r="M10">
-        <v>5.12</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.03001172332942556</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.1903345724907063</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>5.12</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.03001172332942556</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.1903345724907063</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>3.03</v>
+        <v>7.98</v>
       </c>
       <c r="V10">
-        <v>0.01776084407971864</v>
+        <v>0.4178010471204188</v>
       </c>
       <c r="W10">
-        <v>0.2136616362192216</v>
+        <v>-0.02472089314194577</v>
       </c>
       <c r="X10">
-        <v>0.04154960615806658</v>
+        <v>0.07124623056233365</v>
       </c>
       <c r="Y10">
-        <v>0.172112030061155</v>
+        <v>-0.09596712370427941</v>
       </c>
       <c r="Z10">
-        <v>0.2593679157220962</v>
+        <v>0.09249219648431081</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.037781938601662</v>
+        <v>0.07064572435969466</v>
       </c>
       <c r="AC10">
-        <v>-0.037781938601662</v>
+        <v>-0.07064572435969466</v>
       </c>
       <c r="AD10">
-        <v>56.9</v>
+        <v>0.552</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>56.9</v>
+        <v>0.552</v>
       </c>
       <c r="AG10">
-        <v>53.87</v>
+        <v>-7.428000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.2501098901098901</v>
+        <v>0.0280887441481783</v>
       </c>
       <c r="AI10">
-        <v>0.254586129753915</v>
+        <v>0.009541588881974695</v>
       </c>
       <c r="AJ10">
-        <v>0.2399875261727625</v>
+        <v>-0.6363947909527073</v>
       </c>
       <c r="AK10">
-        <v>0.244341633782374</v>
+        <v>-0.1489412897016362</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1665,7 +1668,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JihSun Financial Holding Co.,Ltd. (TPEX:5820)</t>
+          <t>Concord International Securities Co., Ltd (TPEX:5864)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1674,10 +1677,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.11</v>
-      </c>
-      <c r="E11">
-        <v>0.215</v>
+        <v>-0.152</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>144.2</v>
+        <v>-2.61</v>
       </c>
       <c r="L11">
-        <v>0.3381801125703565</v>
+        <v>-0.4015384615384615</v>
       </c>
       <c r="M11">
-        <v>53.6858</v>
+        <v>4.75</v>
       </c>
       <c r="N11">
-        <v>0.03144301276795127</v>
+        <v>0.05337078651685393</v>
       </c>
       <c r="O11">
-        <v>0.3723009708737864</v>
+        <v>-1.81992337164751</v>
       </c>
       <c r="P11">
-        <v>53.6858</v>
+        <v>4.75</v>
       </c>
       <c r="Q11">
-        <v>0.03144301276795127</v>
+        <v>0.05337078651685393</v>
       </c>
       <c r="R11">
-        <v>0.3723009708737864</v>
+        <v>-1.81992337164751</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1722,55 +1722,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>917.2</v>
+        <v>4.09</v>
       </c>
       <c r="V11">
-        <v>0.5371910507203935</v>
+        <v>0.04595505617977528</v>
       </c>
       <c r="W11">
-        <v>0.08935985623102187</v>
+        <v>-0.01566626650660264</v>
       </c>
       <c r="X11">
-        <v>0.0537195874122673</v>
+        <v>0.07658480717175317</v>
       </c>
       <c r="Y11">
-        <v>0.03564026881875457</v>
+        <v>-0.0922510736783558</v>
       </c>
       <c r="Z11">
-        <v>0.1921274601686973</v>
+        <v>0.02948246927019549</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03778944141908111</v>
+        <v>0.07142540497335687</v>
       </c>
       <c r="AC11">
-        <v>-0.03778944141908111</v>
+        <v>-0.07142540497335687</v>
       </c>
       <c r="AD11">
-        <v>1813.5</v>
+        <v>21.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1813.5</v>
+        <v>21.3</v>
       </c>
       <c r="AG11">
-        <v>896.3</v>
+        <v>17.21</v>
       </c>
       <c r="AH11">
-        <v>0.515067170325769</v>
+        <v>0.1931097008159565</v>
       </c>
       <c r="AI11">
-        <v>0.4925713664883071</v>
+        <v>0.1400394477317554</v>
       </c>
       <c r="AJ11">
-        <v>0.3442408879671237</v>
+        <v>0.1620374729309858</v>
       </c>
       <c r="AK11">
-        <v>0.3242177608970881</v>
+        <v>0.1162759273022093</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Concord Securities Co.,Ltd. (TPEX:6016)</t>
+          <t>Horizon Securities Co., Ltd. (TPEX:6015)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.145</v>
+        <v>0.0535</v>
       </c>
       <c r="E12">
-        <v>1.232</v>
+        <v>-0.0313</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1814,28 +1814,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>43.2</v>
+        <v>2.95</v>
       </c>
       <c r="L12">
-        <v>0.3081312410841655</v>
+        <v>0.09161490683229813</v>
       </c>
       <c r="M12">
-        <v>26.1</v>
+        <v>18.8</v>
       </c>
       <c r="N12">
-        <v>0.08118195956454122</v>
+        <v>0.1874376869391825</v>
       </c>
       <c r="O12">
-        <v>0.6041666666666666</v>
+        <v>6.372881355932203</v>
       </c>
       <c r="P12">
-        <v>26.1</v>
+        <v>18.8</v>
       </c>
       <c r="Q12">
-        <v>0.08118195956454122</v>
+        <v>0.1874376869391825</v>
       </c>
       <c r="R12">
-        <v>0.6041666666666666</v>
+        <v>6.372881355932203</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1844,55 +1844,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>45.2</v>
+        <v>78.2</v>
       </c>
       <c r="V12">
-        <v>0.1405909797822706</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="W12">
-        <v>0.1603563474387528</v>
+        <v>0.01606753812636166</v>
       </c>
       <c r="X12">
-        <v>0.06803901011040928</v>
+        <v>0.1083030348234846</v>
       </c>
       <c r="Y12">
-        <v>0.09231733732834352</v>
+        <v>-0.09223549669712297</v>
       </c>
       <c r="Z12">
-        <v>0.2750637629978419</v>
+        <v>0.1161616161616161</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.03829006218431669</v>
+        <v>0.07333990751524619</v>
       </c>
       <c r="AC12">
-        <v>-0.03829006218431669</v>
+        <v>-0.07333990751524619</v>
       </c>
       <c r="AD12">
-        <v>617.1</v>
+        <v>149.4</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>617.1</v>
+        <v>149.4</v>
       </c>
       <c r="AG12">
-        <v>571.9</v>
+        <v>71.2</v>
       </c>
       <c r="AH12">
-        <v>0.6574685702109525</v>
+        <v>0.5983179815778935</v>
       </c>
       <c r="AI12">
-        <v>0.6719294425087108</v>
+        <v>0.506956226671191</v>
       </c>
       <c r="AJ12">
-        <v>0.6401387956122677</v>
+        <v>0.4151603498542274</v>
       </c>
       <c r="AK12">
-        <v>0.6549473202015574</v>
+        <v>0.3288683602771363</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital Securities Corporation (TWSE:6005)</t>
+          <t>Grand Fortune Securities Co.,Ltd (TPEX:6026)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.143</v>
+        <v>0.0165</v>
       </c>
       <c r="E13">
-        <v>0.257</v>
+        <v>-0.095</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1936,28 +1936,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>188.1</v>
+        <v>6.79</v>
       </c>
       <c r="L13">
-        <v>0.4155987627043747</v>
+        <v>0.2581749049429658</v>
       </c>
       <c r="M13">
-        <v>95.2</v>
+        <v>12.2468</v>
       </c>
       <c r="N13">
-        <v>0.07176240012060908</v>
+        <v>0.1039626485568761</v>
       </c>
       <c r="O13">
-        <v>0.5061137692716641</v>
+        <v>1.803652430044183</v>
       </c>
       <c r="P13">
-        <v>95.2</v>
+        <v>12.2468</v>
       </c>
       <c r="Q13">
-        <v>0.07176240012060908</v>
+        <v>0.1039626485568761</v>
       </c>
       <c r="R13">
-        <v>0.5061137692716641</v>
+        <v>1.803652430044183</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1966,55 +1966,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>365.7</v>
+        <v>24.4</v>
       </c>
       <c r="V13">
-        <v>0.2756671189507011</v>
+        <v>0.2071307300509338</v>
       </c>
       <c r="W13">
-        <v>0.1574453837783544</v>
+        <v>0.0405857740585774</v>
       </c>
       <c r="X13">
-        <v>0.06819476749036538</v>
+        <v>0.1250658548701211</v>
       </c>
       <c r="Y13">
-        <v>0.089250616287989</v>
+        <v>-0.08448008081154368</v>
       </c>
       <c r="Z13">
-        <v>0.155</v>
+        <v>0.07915964363111004</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.03829389630546963</v>
+        <v>0.07373795415324459</v>
       </c>
       <c r="AC13">
-        <v>-0.03829389630546963</v>
+        <v>-0.07373795415324459</v>
       </c>
       <c r="AD13">
-        <v>2558.7</v>
+        <v>253.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>2558.7</v>
+        <v>253.3</v>
       </c>
       <c r="AG13">
-        <v>2193</v>
+        <v>228.9</v>
       </c>
       <c r="AH13">
-        <v>0.6585591846189484</v>
+        <v>0.6825653462678524</v>
       </c>
       <c r="AI13">
-        <v>0.638605336062096</v>
+        <v>0.6258957252285643</v>
       </c>
       <c r="AJ13">
-        <v>0.6230821684282305</v>
+        <v>0.6602249783674647</v>
       </c>
       <c r="AK13">
-        <v>0.602307058500412</v>
+        <v>0.6018932421772285</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>China Bills Finance Corporation (TWSE:2820)</t>
+          <t>Concord Securities Co., Ltd. (TPEX:6016)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0125</v>
+        <v>0.0262</v>
       </c>
       <c r="E14">
-        <v>0.00962</v>
+        <v>0.103</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2058,28 +2058,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>65.7</v>
+        <v>12</v>
       </c>
       <c r="L14">
-        <v>0.6441176470588236</v>
+        <v>0.1438848920863309</v>
       </c>
       <c r="M14">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="N14">
-        <v>0.05043227665706052</v>
+        <v>0.1548318206086492</v>
       </c>
       <c r="O14">
-        <v>0.639269406392694</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="P14">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="Q14">
-        <v>0.05043227665706052</v>
+        <v>0.1548318206086492</v>
       </c>
       <c r="R14">
-        <v>0.639269406392694</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2088,179 +2088,60 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>12.3</v>
+        <v>56.3</v>
       </c>
       <c r="V14">
-        <v>0.01476945244956773</v>
+        <v>0.3005872931126535</v>
       </c>
       <c r="W14">
-        <v>0.07708553326293559</v>
+        <v>0.04009355162044771</v>
       </c>
       <c r="X14">
-        <v>0.1902343152661335</v>
+        <v>0.1374675967143931</v>
       </c>
       <c r="Y14">
-        <v>-0.1131487820031979</v>
+        <v>-0.09737404509394541</v>
       </c>
       <c r="Z14">
-        <v>0.01332673093983504</v>
+        <v>0.09573002754820936</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.03915077576314496</v>
+        <v>0.07393941718678711</v>
       </c>
       <c r="AC14">
-        <v>-0.03915077576314496</v>
+        <v>-0.07393941718678711</v>
       </c>
       <c r="AD14">
-        <v>7691.1</v>
+        <v>494.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>7691.1</v>
+        <v>494.3</v>
       </c>
       <c r="AG14">
-        <v>7678.8</v>
+        <v>438</v>
       </c>
       <c r="AH14">
-        <v>0.9022982437616585</v>
+        <v>0.7252053990610329</v>
       </c>
       <c r="AI14">
-        <v>0.8939085763432862</v>
+        <v>0.6751809862040705</v>
       </c>
       <c r="AJ14">
-        <v>0.9021570562526434</v>
+        <v>0.7004637773868544</v>
       </c>
       <c r="AK14">
-        <v>0.8937566925834536</v>
+        <v>0.648120745782776</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Horizon Securities Co., Ltd. (TPEX:6015)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.376</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>48.7</v>
-      </c>
-      <c r="L15">
-        <v>0.4959266802443992</v>
-      </c>
-      <c r="M15">
-        <v>5.94</v>
-      </c>
-      <c r="N15">
-        <v>0.02680505415162455</v>
-      </c>
-      <c r="O15">
-        <v>0.1219712525667351</v>
-      </c>
-      <c r="P15">
-        <v>5.94</v>
-      </c>
-      <c r="Q15">
-        <v>0.02680505415162455</v>
-      </c>
-      <c r="R15">
-        <v>0.1219712525667351</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>102.9</v>
-      </c>
-      <c r="V15">
-        <v>0.4643501805054152</v>
-      </c>
-      <c r="W15">
-        <v>0.3645209580838324</v>
-      </c>
-      <c r="X15">
-        <v>0.05078974885598181</v>
-      </c>
-      <c r="Y15">
-        <v>0.3137312092278506</v>
-      </c>
-      <c r="Z15">
-        <v>0.2551975051975052</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.0393671858256943</v>
-      </c>
-      <c r="AC15">
-        <v>-0.0393671858256943</v>
-      </c>
-      <c r="AD15">
-        <v>196.5</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>196.5</v>
-      </c>
-      <c r="AG15">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="AH15">
-        <v>0.469983257593877</v>
-      </c>
-      <c r="AI15">
-        <v>0.5169692186266771</v>
-      </c>
-      <c r="AJ15">
-        <v>0.2969543147208122</v>
-      </c>
-      <c r="AK15">
-        <v>0.3376623376623377</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/taiwan/taiwan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0296</v>
+        <v>0.0493</v>
       </c>
       <c r="E2">
-        <v>-0.0378</v>
+        <v>0.0907</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>201.457</v>
+        <v>415.067</v>
       </c>
       <c r="L2">
-        <v>0.2140449856033319</v>
+        <v>0.3993332691937656</v>
       </c>
       <c r="M2">
-        <v>357.1968</v>
+        <v>131.9662</v>
       </c>
       <c r="N2">
-        <v>0.09589433273376466</v>
+        <v>0.02758663795806593</v>
       </c>
       <c r="O2">
-        <v>1.773067205408598</v>
+        <v>0.3179395133797676</v>
       </c>
       <c r="P2">
-        <v>357.1968</v>
+        <v>131.9662</v>
       </c>
       <c r="Q2">
-        <v>0.09589433273376466</v>
+        <v>0.02758663795806593</v>
       </c>
       <c r="R2">
-        <v>1.773067205408598</v>
+        <v>0.3179395133797676</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1326.77</v>
+        <v>1256.41</v>
       </c>
       <c r="V2">
-        <v>0.3561894279041048</v>
+        <v>0.2626439785103581</v>
       </c>
       <c r="W2">
-        <v>0.03562130934776327</v>
+        <v>0.09610320214914603</v>
       </c>
       <c r="X2">
-        <v>0.09002603668249065</v>
+        <v>0.07369044450041637</v>
       </c>
       <c r="Y2">
-        <v>-0.05440472733472738</v>
+        <v>0.02241275764872966</v>
       </c>
       <c r="Z2">
-        <v>0.05717737707963504</v>
+        <v>0.08035714630853077</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07039726900506925</v>
+        <v>0.05920860317288394</v>
       </c>
       <c r="AC2">
-        <v>-0.07039726900506925</v>
+        <v>-0.05920860317288394</v>
       </c>
       <c r="AD2">
-        <v>10082.152</v>
+        <v>11976.28</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10082.152</v>
+        <v>11976.28</v>
       </c>
       <c r="AG2">
-        <v>8755.382</v>
+        <v>10719.87</v>
       </c>
       <c r="AH2">
-        <v>0.7302175728750786</v>
+        <v>0.7145760317136417</v>
       </c>
       <c r="AI2">
-        <v>0.6969140211014808</v>
+        <v>0.7143330899790524</v>
       </c>
       <c r="AJ2">
-        <v>0.7015371928294569</v>
+        <v>0.6914452606722195</v>
       </c>
       <c r="AK2">
-        <v>0.6663110625945866</v>
+        <v>0.6911911392347931</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0247</v>
+        <v>-0.0183</v>
       </c>
       <c r="E3">
-        <v>0.00136</v>
+        <v>-0.0264</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>42.1</v>
+        <v>37.4</v>
       </c>
       <c r="L3">
-        <v>0.7246127366609294</v>
+        <v>0.6101141924959217</v>
       </c>
       <c r="M3">
-        <v>38</v>
+        <v>20.9</v>
       </c>
       <c r="N3">
-        <v>0.05994636377977599</v>
+        <v>0.03157576673213476</v>
       </c>
       <c r="O3">
-        <v>0.9026128266033254</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="P3">
-        <v>38</v>
+        <v>20.9</v>
       </c>
       <c r="Q3">
-        <v>0.05994636377977599</v>
+        <v>0.03157576673213476</v>
       </c>
       <c r="R3">
-        <v>0.9026128266033254</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>35.2</v>
+        <v>13.4</v>
       </c>
       <c r="V3">
-        <v>0.05552926329073987</v>
+        <v>0.02024474996222994</v>
       </c>
       <c r="W3">
-        <v>0.04612182296231376</v>
+        <v>0.055</v>
       </c>
       <c r="X3">
-        <v>0.2923229965925215</v>
+        <v>0.2126936557657356</v>
       </c>
       <c r="Y3">
-        <v>-0.2462011736302077</v>
+        <v>-0.1576936557657356</v>
       </c>
       <c r="Z3">
-        <v>0.006762419107034778</v>
+        <v>0.009908031485881458</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06922506371491288</v>
+        <v>0.05839850067805641</v>
       </c>
       <c r="AC3">
-        <v>-0.06922506371491288</v>
+        <v>-0.05839850067805641</v>
       </c>
       <c r="AD3">
-        <v>5542.1</v>
+        <v>5958.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5542.1</v>
+        <v>5958.5</v>
       </c>
       <c r="AG3">
-        <v>5506.900000000001</v>
+        <v>5945.1</v>
       </c>
       <c r="AH3">
-        <v>0.8973607512953369</v>
+        <v>0.9000211467585041</v>
       </c>
       <c r="AI3">
-        <v>0.8907121389884444</v>
+        <v>0.8913371927777529</v>
       </c>
       <c r="AJ3">
-        <v>0.8967724075039083</v>
+        <v>0.8998183744513395</v>
       </c>
       <c r="AK3">
-        <v>0.8900903521957685</v>
+        <v>0.8911189387693923</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0405</v>
+        <v>0.0315</v>
       </c>
       <c r="E4">
-        <v>-0.04849999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>52.3</v>
+        <v>119.6</v>
       </c>
       <c r="L4">
-        <v>0.1842847075405215</v>
+        <v>0.3846896108073335</v>
       </c>
       <c r="M4">
-        <v>117.3</v>
+        <v>34.9</v>
       </c>
       <c r="N4">
-        <v>0.1529933481152993</v>
+        <v>0.03012516184721623</v>
       </c>
       <c r="O4">
-        <v>2.24282982791587</v>
+        <v>0.2918060200668897</v>
       </c>
       <c r="P4">
-        <v>117.3</v>
+        <v>34.9</v>
       </c>
       <c r="Q4">
-        <v>0.1529933481152993</v>
+        <v>0.03012516184721623</v>
       </c>
       <c r="R4">
-        <v>2.24282982791587</v>
+        <v>0.2918060200668897</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>366.1</v>
+        <v>287.5</v>
       </c>
       <c r="V4">
-        <v>0.4775009782183383</v>
+        <v>0.2481657315494173</v>
       </c>
       <c r="W4">
-        <v>0.0387120651369356</v>
+        <v>0.1097449073224445</v>
       </c>
       <c r="X4">
-        <v>0.1553998164405579</v>
+        <v>0.1079415791966446</v>
       </c>
       <c r="Y4">
-        <v>-0.1166877513036223</v>
+        <v>0.001803328125799933</v>
       </c>
       <c r="Z4">
-        <v>0.08271399842616071</v>
+        <v>0.09745165031501737</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06940800634900479</v>
+        <v>0.05868602862409129</v>
       </c>
       <c r="AC4">
-        <v>-0.06940800634900479</v>
+        <v>-0.05868602862409129</v>
       </c>
       <c r="AD4">
-        <v>2565.3</v>
+        <v>3274.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2565.3</v>
+        <v>3274.3</v>
       </c>
       <c r="AG4">
-        <v>2199.2</v>
+        <v>2986.8</v>
       </c>
       <c r="AH4">
-        <v>0.7698979591836735</v>
+        <v>0.7386527702580762</v>
       </c>
       <c r="AI4">
-        <v>0.6850299081392865</v>
+        <v>0.7156157796962082</v>
       </c>
       <c r="AJ4">
-        <v>0.7414949930881014</v>
+        <v>0.7205268617470388</v>
       </c>
       <c r="AK4">
-        <v>0.6509012342025039</v>
+        <v>0.6965485074626866</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>President Securities Corporation (TWSE:2855)</t>
+          <t>Concord Securities Co., Ltd. (TPEX:6016)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.033</v>
+        <v>0.0984</v>
       </c>
       <c r="E5">
-        <v>-0.0592</v>
+        <v>0.6579999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,85 +972,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>36.2</v>
+        <v>34.3</v>
       </c>
       <c r="L5">
-        <v>0.173621103117506</v>
+        <v>0.3402777777777777</v>
       </c>
       <c r="M5">
-        <v>86.59999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1167745415318231</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>2.392265193370165</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>86.59999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.1167745415318231</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>2.392265193370165</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>202.5</v>
+        <v>126</v>
       </c>
       <c r="V5">
-        <v>0.2730582524271845</v>
+        <v>0.4671857619577308</v>
       </c>
       <c r="W5">
-        <v>0.03253055355859095</v>
+        <v>0.1453389830508474</v>
       </c>
       <c r="X5">
-        <v>0.09970129960236448</v>
+        <v>0.09641612572013794</v>
       </c>
       <c r="Y5">
-        <v>-0.06717074604377354</v>
+        <v>0.0489228573307095</v>
       </c>
       <c r="Z5">
-        <v>0.1046902223851295</v>
+        <v>0.1495548961424332</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06974516290661031</v>
+        <v>0.05878658139344359</v>
       </c>
       <c r="AC5">
-        <v>-0.06974516290661031</v>
+        <v>-0.05878658139344359</v>
       </c>
       <c r="AD5">
-        <v>853.2</v>
+        <v>579</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>853.2</v>
+        <v>579</v>
       </c>
       <c r="AG5">
-        <v>650.7</v>
+        <v>453</v>
       </c>
       <c r="AH5">
-        <v>0.5349887133182843</v>
+        <v>0.6822198656769176</v>
       </c>
       <c r="AI5">
-        <v>0.4790567097136441</v>
+        <v>0.6764018691588785</v>
       </c>
       <c r="AJ5">
-        <v>0.4673561732385261</v>
+        <v>0.626816106268161</v>
       </c>
       <c r="AK5">
-        <v>0.4122267975926513</v>
+        <v>0.6205479452054794</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Good Finance Securities Co., Ltd. (TPEX:6021)</t>
+          <t>President Securities Corporation (TWSE:2855)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1073,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.122</v>
+        <v>0.0445</v>
       </c>
       <c r="E6">
-        <v>-0.0443</v>
+        <v>0.0525</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,82 +1091,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3.34</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L6">
-        <v>0.1113333333333333</v>
+        <v>0.3281868566904197</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>17.6</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.0188497376030845</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.2123039806996381</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>17.6</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.0188497376030845</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.2123039806996381</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>24.7</v>
+        <v>177.9</v>
       </c>
       <c r="V6">
-        <v>0.1218549580661075</v>
+        <v>0.1905322908857235</v>
       </c>
       <c r="W6">
-        <v>0.01674185463659148</v>
+        <v>0.08960224816255945</v>
       </c>
       <c r="X6">
-        <v>0.0803507737626168</v>
+        <v>0.08840494434088611</v>
       </c>
       <c r="Y6">
-        <v>-0.06360891912602533</v>
+        <v>0.001197303821673337</v>
       </c>
       <c r="Z6">
-        <v>0.09406157898037248</v>
+        <v>0.1604237320428304</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07011197555071585</v>
+        <v>0.05888657418898477</v>
       </c>
       <c r="AC6">
-        <v>-0.07011197555071585</v>
+        <v>-0.05888657418898477</v>
       </c>
       <c r="AD6">
-        <v>78.59999999999999</v>
+        <v>1563.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>78.59999999999999</v>
+        <v>1563.5</v>
       </c>
       <c r="AG6">
-        <v>53.89999999999999</v>
+        <v>1385.6</v>
       </c>
       <c r="AH6">
-        <v>0.2794169925346605</v>
+        <v>0.6261012333813872</v>
       </c>
       <c r="AI6">
-        <v>0.3504235399019171</v>
+        <v>0.6134018596257209</v>
       </c>
       <c r="AJ6">
-        <v>0.2100545596258769</v>
+        <v>0.5974216358383995</v>
       </c>
       <c r="AK6">
-        <v>0.2700400801603207</v>
+        <v>0.5843947701391817</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TaChan Securities Co.,Ltd. (TPEX:6020)</t>
+          <t>Horizon Securities Co., Ltd. (TPEX:6015)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1195,10 +1195,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.07690000000000001</v>
-      </c>
-      <c r="E7">
-        <v>-0.64</v>
+        <v>0.16</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1213,85 +1210,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0.037</v>
+        <v>0.657</v>
       </c>
       <c r="L7">
-        <v>0.005727554179566563</v>
+        <v>0.02175496688741722</v>
       </c>
       <c r="M7">
-        <v>18.9</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.1236910994764398</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>510.8108108108108</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>18.9</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.1236910994764398</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>510.8108108108108</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>53.4</v>
+        <v>61.8</v>
       </c>
       <c r="V7">
-        <v>0.3494764397905759</v>
+        <v>0.4835680751173709</v>
       </c>
       <c r="W7">
-        <v>0.0002219556088782244</v>
+        <v>0.004521679284239504</v>
       </c>
       <c r="X7">
-        <v>0.07979446476153527</v>
+        <v>0.08471480503498716</v>
       </c>
       <c r="Y7">
-        <v>-0.07957250915265705</v>
+        <v>-0.08019312575074765</v>
       </c>
       <c r="Z7">
-        <v>0.03995052566481138</v>
+        <v>0.1394919168591224</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07012857925631025</v>
+        <v>0.05894556567938709</v>
       </c>
       <c r="AC7">
-        <v>-0.07012857925631025</v>
+        <v>-0.05894556567938709</v>
       </c>
       <c r="AD7">
-        <v>55.9</v>
+        <v>186.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>55.9</v>
+        <v>186.2</v>
       </c>
       <c r="AG7">
-        <v>2.5</v>
+        <v>124.4</v>
       </c>
       <c r="AH7">
-        <v>0.2678485864877815</v>
+        <v>0.5929936305732484</v>
       </c>
       <c r="AI7">
-        <v>0.3052976515565265</v>
+        <v>0.5608433734939758</v>
       </c>
       <c r="AJ7">
-        <v>0.01609787508048937</v>
+        <v>0.493259318001586</v>
       </c>
       <c r="AK7">
-        <v>0.01927525057825752</v>
+        <v>0.46039970392302</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1308,7 +1302,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yuanta Futures Co., Ltd. (TPEX:6023)</t>
+          <t>Grand Fortune Securities Co.,Ltd (TPEX:6026)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1317,10 +1311,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0604</v>
+        <v>0.0858</v>
       </c>
       <c r="E8">
-        <v>0.0282</v>
+        <v>0.146</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1335,28 +1329,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>29.9</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>0.2521079258010118</v>
+        <v>0.459016393442623</v>
       </c>
       <c r="M8">
-        <v>21</v>
+        <v>11.9</v>
       </c>
       <c r="N8">
-        <v>0.04545454545454546</v>
+        <v>0.07134292565947242</v>
       </c>
       <c r="O8">
-        <v>0.7023411371237459</v>
+        <v>0.85</v>
       </c>
       <c r="P8">
-        <v>21</v>
+        <v>11.9</v>
       </c>
       <c r="Q8">
-        <v>0.04545454545454546</v>
+        <v>0.07134292565947242</v>
       </c>
       <c r="R8">
-        <v>0.7023411371237459</v>
+        <v>0.85</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1365,55 +1359,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>298.5</v>
+        <v>27.3</v>
       </c>
       <c r="V8">
-        <v>0.6461038961038961</v>
+        <v>0.1636690647482014</v>
       </c>
       <c r="W8">
-        <v>0.06913294797687861</v>
+        <v>0.09831460674157302</v>
       </c>
       <c r="X8">
-        <v>0.07337953926997595</v>
+        <v>0.07513349982695128</v>
       </c>
       <c r="Y8">
-        <v>-0.004246591293097346</v>
+        <v>0.02318110691462175</v>
       </c>
       <c r="Z8">
-        <v>0.7538295302866583</v>
+        <v>0.08214381901427416</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07036730894981515</v>
+        <v>0.05916207485232679</v>
       </c>
       <c r="AC8">
-        <v>-0.07036730894981515</v>
+        <v>-0.05916207485232679</v>
       </c>
       <c r="AD8">
-        <v>52.2</v>
+        <v>148.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>52.2</v>
+        <v>148.8</v>
       </c>
       <c r="AG8">
-        <v>-246.3</v>
+        <v>121.5</v>
       </c>
       <c r="AH8">
-        <v>0.1015169194865811</v>
+        <v>0.4714828897338403</v>
       </c>
       <c r="AI8">
-        <v>0.1166219839142091</v>
+        <v>0.4582691715429627</v>
       </c>
       <c r="AJ8">
-        <v>-1.141863699582754</v>
+        <v>0.421436004162331</v>
       </c>
       <c r="AK8">
-        <v>-1.651911468812878</v>
+        <v>0.4085406859448554</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1430,7 +1424,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital Futures Corporation (TWSE:6024)</t>
+          <t>Good Finance Securities Co., Ltd. (TPEX:6021)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1439,10 +1433,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.00544</v>
+        <v>0.0541</v>
       </c>
       <c r="E9">
-        <v>-0.0159</v>
+        <v>-0.13</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1457,28 +1451,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>3.65</v>
       </c>
       <c r="L9">
-        <v>0.2447980416156671</v>
+        <v>0.1336996336996337</v>
       </c>
       <c r="M9">
-        <v>10.6</v>
+        <v>2.8062</v>
       </c>
       <c r="N9">
-        <v>0.04211362733412793</v>
+        <v>0.01831723237597912</v>
       </c>
       <c r="O9">
-        <v>0.53</v>
+        <v>0.7688219178082192</v>
       </c>
       <c r="P9">
-        <v>10.6</v>
+        <v>2.8062</v>
       </c>
       <c r="Q9">
-        <v>0.04211362733412793</v>
+        <v>0.01831723237597912</v>
       </c>
       <c r="R9">
-        <v>0.53</v>
+        <v>0.7688219178082192</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1487,55 +1481,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>175.4</v>
+        <v>11.1</v>
       </c>
       <c r="V9">
-        <v>0.6968613428684943</v>
+        <v>0.07245430809399478</v>
       </c>
       <c r="W9">
-        <v>0.09045680687471733</v>
+        <v>0.02505147563486616</v>
       </c>
       <c r="X9">
-        <v>0.07212575203915733</v>
+        <v>0.07224738917388146</v>
       </c>
       <c r="Y9">
-        <v>0.01833105483556</v>
+        <v>-0.0471959135390153</v>
       </c>
       <c r="Z9">
-        <v>1.751677708453936</v>
+        <v>0.1378927164360036</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07042722906032335</v>
+        <v>0.05925513149344108</v>
       </c>
       <c r="AC9">
-        <v>-0.07042722906032335</v>
+        <v>-0.05925513149344108</v>
       </c>
       <c r="AD9">
-        <v>16</v>
+        <v>110.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>16</v>
+        <v>110.6</v>
       </c>
       <c r="AG9">
-        <v>-159.4</v>
+        <v>99.5</v>
       </c>
       <c r="AH9">
-        <v>0.05976839745984311</v>
+        <v>0.419257012888552</v>
       </c>
       <c r="AI9">
-        <v>0.07191011235955057</v>
+        <v>0.3982715160244868</v>
       </c>
       <c r="AJ9">
-        <v>-1.726977248104009</v>
+        <v>0.3937475267115156</v>
       </c>
       <c r="AK9">
-        <v>-3.384288747346073</v>
+        <v>0.373218304576144</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1552,7 +1546,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reliance Securities Co.,Ltd. (TPEX:6027)</t>
+          <t>TaChan Securities Co.,Ltd. (TPEX:6020)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1561,7 +1555,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.105</v>
+        <v>0.212</v>
+      </c>
+      <c r="E10">
+        <v>0.436</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1576,10 +1573,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-1.55</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L10">
-        <v>-0.2753108348134991</v>
+        <v>0.6309677419354839</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1588,7 +1585,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1597,61 +1594,61 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>7.98</v>
+        <v>47.5</v>
       </c>
       <c r="V10">
-        <v>0.4178010471204188</v>
+        <v>0.3050738599871548</v>
       </c>
       <c r="W10">
-        <v>-0.02472089314194577</v>
+        <v>0.07694728560188828</v>
       </c>
       <c r="X10">
-        <v>0.07124623056233365</v>
+        <v>0.06733373368044999</v>
       </c>
       <c r="Y10">
-        <v>-0.09596712370427941</v>
+        <v>0.009613551921438285</v>
       </c>
       <c r="Z10">
-        <v>0.09249219648431081</v>
+        <v>0.1195987654320988</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07064572435969466</v>
+        <v>0.05946442887564118</v>
       </c>
       <c r="AC10">
-        <v>-0.07064572435969466</v>
+        <v>-0.05946442887564118</v>
       </c>
       <c r="AD10">
-        <v>0.552</v>
+        <v>67.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.552</v>
+        <v>67.3</v>
       </c>
       <c r="AG10">
-        <v>-7.428000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="AH10">
-        <v>0.0280887441481783</v>
+        <v>0.3017937219730942</v>
       </c>
       <c r="AI10">
-        <v>0.009541588881974695</v>
+        <v>0.3224724484906564</v>
       </c>
       <c r="AJ10">
-        <v>-0.6363947909527073</v>
+        <v>0.1128205128205128</v>
       </c>
       <c r="AK10">
-        <v>-0.1489412897016362</v>
+        <v>0.1228287841191067</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1668,7 +1665,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Concord International Securities Co., Ltd (TPEX:5864)</t>
+          <t>Yuanta Futures Co., Ltd. (TPEX:6023)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1677,7 +1674,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.152</v>
+        <v>-0.00386</v>
+      </c>
+      <c r="E11">
+        <v>0.13</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-2.61</v>
+        <v>54.1</v>
       </c>
       <c r="L11">
-        <v>-0.4015384615384615</v>
+        <v>0.5497967479674797</v>
       </c>
       <c r="M11">
-        <v>4.75</v>
+        <v>22.5</v>
       </c>
       <c r="N11">
-        <v>0.05337078651685393</v>
+        <v>0.0391644908616188</v>
       </c>
       <c r="O11">
-        <v>-1.81992337164751</v>
+        <v>0.4158964879852126</v>
       </c>
       <c r="P11">
-        <v>4.75</v>
+        <v>22.5</v>
       </c>
       <c r="Q11">
-        <v>0.05337078651685393</v>
+        <v>0.0391644908616188</v>
       </c>
       <c r="R11">
-        <v>-1.81992337164751</v>
+        <v>0.4158964879852126</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1722,55 +1722,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>4.09</v>
+        <v>329.8</v>
       </c>
       <c r="V11">
-        <v>0.04595505617977528</v>
+        <v>0.5740644038294169</v>
       </c>
       <c r="W11">
-        <v>-0.01566626650660264</v>
+        <v>0.1368234699038948</v>
       </c>
       <c r="X11">
-        <v>0.07658480717175317</v>
+        <v>0.06147248048668469</v>
       </c>
       <c r="Y11">
-        <v>-0.0922510736783558</v>
+        <v>0.07535098941721011</v>
       </c>
       <c r="Z11">
-        <v>0.02948246927019549</v>
+        <v>0.6599597585513081</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07142540497335687</v>
+        <v>0.0598600343556291</v>
       </c>
       <c r="AC11">
-        <v>-0.07142540497335687</v>
+        <v>-0.0598600343556291</v>
       </c>
       <c r="AD11">
-        <v>21.3</v>
+        <v>49.8</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>21.3</v>
+        <v>49.8</v>
       </c>
       <c r="AG11">
-        <v>17.21</v>
+        <v>-280</v>
       </c>
       <c r="AH11">
-        <v>0.1931097008159565</v>
+        <v>0.07976934166266218</v>
       </c>
       <c r="AI11">
-        <v>0.1400394477317554</v>
+        <v>0.1017364657814096</v>
       </c>
       <c r="AJ11">
-        <v>0.1620374729309858</v>
+        <v>-0.9507640067911715</v>
       </c>
       <c r="AK11">
-        <v>0.1162759273022093</v>
+        <v>-1.753287413901065</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Horizon Securities Co., Ltd. (TPEX:6015)</t>
+          <t>Capital Futures Corporation (TWSE:6024)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0535</v>
+        <v>-0.0495</v>
       </c>
       <c r="E12">
-        <v>-0.0313</v>
+        <v>0.02</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1814,28 +1814,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>2.95</v>
+        <v>31.3</v>
       </c>
       <c r="L12">
-        <v>0.09161490683229813</v>
+        <v>0.435326842837274</v>
       </c>
       <c r="M12">
-        <v>18.8</v>
+        <v>19.7</v>
       </c>
       <c r="N12">
-        <v>0.1874376869391825</v>
+        <v>0.05612535612535612</v>
       </c>
       <c r="O12">
-        <v>6.372881355932203</v>
+        <v>0.6293929712460063</v>
       </c>
       <c r="P12">
-        <v>18.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q12">
-        <v>0.1874376869391825</v>
+        <v>0.05612535612535612</v>
       </c>
       <c r="R12">
-        <v>6.372881355932203</v>
+        <v>0.6293929712460063</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1844,55 +1844,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>78.2</v>
+        <v>169.7</v>
       </c>
       <c r="V12">
-        <v>0.7796610169491526</v>
+        <v>0.4834757834757835</v>
       </c>
       <c r="W12">
-        <v>0.01606753812636166</v>
+        <v>0.1516472868217054</v>
       </c>
       <c r="X12">
-        <v>0.1083030348234846</v>
+        <v>0.06024088895407466</v>
       </c>
       <c r="Y12">
-        <v>-0.09223549669712297</v>
+        <v>0.09140639786763076</v>
       </c>
       <c r="Z12">
-        <v>0.1161616161616161</v>
+        <v>1.542488147083432</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.07333990751524619</v>
+        <v>0.05997743894711349</v>
       </c>
       <c r="AC12">
-        <v>-0.07333990751524619</v>
+        <v>-0.05997743894711349</v>
       </c>
       <c r="AD12">
-        <v>149.4</v>
+        <v>4.94</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>149.4</v>
+        <v>4.94</v>
       </c>
       <c r="AG12">
-        <v>71.2</v>
+        <v>-164.76</v>
       </c>
       <c r="AH12">
-        <v>0.5983179815778935</v>
+        <v>0.01387874360847334</v>
       </c>
       <c r="AI12">
-        <v>0.506956226671191</v>
+        <v>0.02225826800036046</v>
       </c>
       <c r="AJ12">
-        <v>0.4151603498542274</v>
+        <v>-0.8846649484536081</v>
       </c>
       <c r="AK12">
-        <v>0.3288683602771363</v>
+        <v>-3.153905053598774</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grand Fortune Securities Co.,Ltd (TPEX:6026)</t>
+          <t>Reliance Securities Co.,Ltd. (TPEX:6027)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0165</v>
+        <v>0.0371</v>
       </c>
       <c r="E13">
-        <v>-0.095</v>
+        <v>0.169</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1936,85 +1936,82 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>6.79</v>
+        <v>5.38</v>
       </c>
       <c r="L13">
-        <v>0.2581749049429658</v>
+        <v>0.4890909090909091</v>
       </c>
       <c r="M13">
-        <v>12.2468</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.1039626485568761</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>1.803652430044183</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>12.2468</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.1039626485568761</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>1.803652430044183</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>24.4</v>
+        <v>1.97</v>
       </c>
       <c r="V13">
-        <v>0.2071307300509338</v>
+        <v>0.03505338078291815</v>
       </c>
       <c r="W13">
-        <v>0.0405857740585774</v>
+        <v>0.09389179755671903</v>
       </c>
       <c r="X13">
-        <v>0.1250658548701211</v>
+        <v>0.06079894723664259</v>
       </c>
       <c r="Y13">
-        <v>-0.08448008081154368</v>
+        <v>0.03309285032007644</v>
       </c>
       <c r="Z13">
-        <v>0.07915964363111004</v>
+        <v>0.2205646454924607</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.07373795415324459</v>
+        <v>0.06022663953993393</v>
       </c>
       <c r="AC13">
-        <v>-0.07373795415324459</v>
+        <v>-0.06022663953993393</v>
       </c>
       <c r="AD13">
-        <v>253.3</v>
+        <v>2.64</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>253.3</v>
+        <v>2.64</v>
       </c>
       <c r="AG13">
-        <v>228.9</v>
+        <v>0.6700000000000002</v>
       </c>
       <c r="AH13">
-        <v>0.6825653462678524</v>
+        <v>0.04486743711760707</v>
       </c>
       <c r="AI13">
-        <v>0.6258957252285643</v>
+        <v>0.04181184668989547</v>
       </c>
       <c r="AJ13">
-        <v>0.6602249783674647</v>
+        <v>0.01178125549498857</v>
       </c>
       <c r="AK13">
-        <v>0.6018932421772285</v>
+        <v>0.01095308157593592</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2031,7 +2028,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Concord Securities Co., Ltd. (TPEX:6016)</t>
+          <t>Concord International Securities Co., Ltd (TPEX:5864)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2040,10 +2037,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0262</v>
+        <v>0.197</v>
       </c>
       <c r="E14">
-        <v>0.103</v>
+        <v>0.0907</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2058,28 +2055,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L14">
-        <v>0.1438848920863309</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="M14">
-        <v>29</v>
+        <v>1.66</v>
       </c>
       <c r="N14">
-        <v>0.1548318206086492</v>
+        <v>0.009502003434459073</v>
       </c>
       <c r="O14">
-        <v>2.416666666666667</v>
+        <v>0.07545454545454545</v>
       </c>
       <c r="P14">
-        <v>29</v>
+        <v>1.66</v>
       </c>
       <c r="Q14">
-        <v>0.1548318206086492</v>
+        <v>0.009502003434459073</v>
       </c>
       <c r="R14">
-        <v>2.416666666666667</v>
+        <v>0.07545454545454545</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2088,55 +2085,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>56.3</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
-        <v>0.3005872931126535</v>
+        <v>0.01396680022896394</v>
       </c>
       <c r="W14">
-        <v>0.04009355162044771</v>
+        <v>0.1681957186544342</v>
       </c>
       <c r="X14">
-        <v>0.1374675967143931</v>
+        <v>0.06298285085568411</v>
       </c>
       <c r="Y14">
-        <v>-0.09737404509394541</v>
+        <v>0.1052128677987501</v>
       </c>
       <c r="Z14">
-        <v>0.09573002754820936</v>
+        <v>0.1959327072495101</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.07393941718678711</v>
+        <v>0.06043080078015109</v>
       </c>
       <c r="AC14">
-        <v>-0.07393941718678711</v>
+        <v>-0.06043080078015109</v>
       </c>
       <c r="AD14">
-        <v>494.3</v>
+        <v>30.7</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>494.3</v>
+        <v>30.7</v>
       </c>
       <c r="AG14">
-        <v>438</v>
+        <v>28.26</v>
       </c>
       <c r="AH14">
-        <v>0.7252053990610329</v>
+        <v>0.1494644595910419</v>
       </c>
       <c r="AI14">
-        <v>0.6751809862040705</v>
+        <v>0.1680350301039956</v>
       </c>
       <c r="AJ14">
-        <v>0.7004637773868544</v>
+        <v>0.1392392589672842</v>
       </c>
       <c r="AK14">
-        <v>0.648120745782776</v>
+        <v>0.1567735493176523</v>
       </c>
       <c r="AL14">
         <v>0</v>
